--- a/Result/profitability/6156.xlsx
+++ b/Result/profitability/6156.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.58</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1075</v>
+        <v>0.11125</v>
       </c>
       <c r="N2" t="n">
-        <v>14.9175</v>
+        <v>14.61625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>0.10125</v>
+        <v>0.003750000000000007</v>
       </c>
       <c r="N3" t="n">
-        <v>13.445</v>
+        <v>12.68875</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.52</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.08249999999999999</v>
+        <v>-0.13</v>
       </c>
       <c r="N4" t="n">
-        <v>11.9675</v>
+        <v>11.11</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-4.07</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.66</v>
+        <v>-0.58625</v>
       </c>
       <c r="N5" t="n">
-        <v>8.65375</v>
+        <v>8.223750000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.67</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.69125</v>
+        <v>-0.6737500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>7.0575</v>
+        <v>7.188750000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7575000000000001</v>
+        <v>-0.77125</v>
       </c>
       <c r="N7" t="n">
-        <v>6.355</v>
+        <v>6.414999999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.12</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8075</v>
+        <v>-0.775</v>
       </c>
       <c r="N8" t="n">
-        <v>6.236249999999999</v>
+        <v>5.92875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6156</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1716</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1488</v>
+      </c>
+      <c r="E75" t="n">
+        <v>228</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>50</v>
+      </c>
+      <c r="J75" t="n">
+        <v>55</v>
+      </c>
+      <c r="K75" t="n">
+        <v>19</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.20125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.76125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-2.888888888888889</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.459999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1560913705583756</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.404761904761905</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.439999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2054958183990441</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
